--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -24223,6 +24223,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1038">
+      <c r="A1038" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1038" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C1038" t="n">
+        <v>0.610000014305115</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>0.579999983310699</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>0.610000014305115</v>
+      </c>
+      <c r="F1038" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="G1038" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -24246,6 +24246,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1039">
+      <c r="A1039" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1039" t="n">
+        <v>14500</v>
+      </c>
+      <c r="C1039" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="F1039" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="G1039" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -24269,6 +24269,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1040">
+      <c r="A1040" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1040" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1040" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="D1040" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="F1040" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="G1040" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1041" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C1041" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="D1041" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="F1041" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="G1041" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -24133,22 +24133,22 @@
     </row>
     <row r="1034">
       <c r="A1034" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1034" t="n">
-        <v>2500</v>
+        <v>9000</v>
       </c>
       <c r="C1034" t="n">
-        <v>0.634999990463257</v>
+        <v>0.610000014305115</v>
       </c>
       <c r="D1034" t="n">
-        <v>0.600000023841858</v>
+        <v>0.605000019073486</v>
       </c>
       <c r="E1034" t="n">
-        <v>0.600000023841858</v>
+        <v>0.610000014305115</v>
       </c>
       <c r="F1034" t="n">
-        <v>0.634999990463257</v>
+        <v>0.610000014305115</v>
       </c>
       <c r="G1034" t="s">
         <v>7</v>
@@ -24156,19 +24156,19 @@
     </row>
     <row r="1035">
       <c r="A1035" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1035" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="C1035" t="n">
         <v>0.634999990463257</v>
       </c>
       <c r="D1035" t="n">
-        <v>0.634999990463257</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="E1035" t="n">
-        <v>0.634999990463257</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="F1035" t="n">
         <v>0.634999990463257</v>
@@ -24179,22 +24179,22 @@
     </row>
     <row r="1036">
       <c r="A1036" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1036" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="C1036" t="n">
-        <v>0.629999995231628</v>
+        <v>0.634999990463257</v>
       </c>
       <c r="D1036" t="n">
-        <v>0.610000014305115</v>
+        <v>0.634999990463257</v>
       </c>
       <c r="E1036" t="n">
-        <v>0.610000014305115</v>
+        <v>0.634999990463257</v>
       </c>
       <c r="F1036" t="n">
-        <v>0.629999995231628</v>
+        <v>0.634999990463257</v>
       </c>
       <c r="G1036" t="s">
         <v>7</v>
@@ -24202,22 +24202,22 @@
     </row>
     <row r="1037">
       <c r="A1037" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1037" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="C1037" t="n">
+        <v>0.629999995231628</v>
+      </c>
+      <c r="D1037" t="n">
         <v>0.610000014305115</v>
-      </c>
-      <c r="D1037" t="n">
-        <v>0.605000019073486</v>
       </c>
       <c r="E1037" t="n">
         <v>0.610000014305115</v>
       </c>
       <c r="F1037" t="n">
-        <v>0.610000014305115</v>
+        <v>0.629999995231628</v>
       </c>
       <c r="G1037" t="s">
         <v>7</v>
@@ -24225,22 +24225,22 @@
     </row>
     <row r="1038">
       <c r="A1038" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1038" t="n">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="C1038" t="n">
         <v>0.610000014305115</v>
       </c>
       <c r="D1038" t="n">
-        <v>0.579999983310699</v>
+        <v>0.605000019073486</v>
       </c>
       <c r="E1038" t="n">
         <v>0.610000014305115</v>
       </c>
       <c r="F1038" t="n">
-        <v>0.600000023841858</v>
+        <v>0.610000014305115</v>
       </c>
       <c r="G1038" t="s">
         <v>7</v>
@@ -24248,19 +24248,19 @@
     </row>
     <row r="1039">
       <c r="A1039" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1039" t="n">
-        <v>14500</v>
+        <v>14000</v>
       </c>
       <c r="C1039" t="n">
-        <v>0.600000023841858</v>
+        <v>0.610000014305115</v>
       </c>
       <c r="D1039" t="n">
-        <v>0.584999978542328</v>
+        <v>0.579999983310699</v>
       </c>
       <c r="E1039" t="n">
-        <v>0.600000023841858</v>
+        <v>0.610000014305115</v>
       </c>
       <c r="F1039" t="n">
         <v>0.600000023841858</v>
@@ -24271,16 +24271,16 @@
     </row>
     <row r="1040">
       <c r="A1040" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1040" t="n">
-        <v>0</v>
+        <v>14500</v>
       </c>
       <c r="C1040" t="n">
         <v>0.600000023841858</v>
       </c>
       <c r="D1040" t="n">
-        <v>0.600000023841858</v>
+        <v>0.584999978542328</v>
       </c>
       <c r="E1040" t="n">
         <v>0.600000023841858</v>
@@ -24294,13 +24294,13 @@
     </row>
     <row r="1041">
       <c r="A1041" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1041" t="n">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="C1041" t="n">
-        <v>0.620000004768372</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="D1041" t="n">
         <v>0.600000023841858</v>
@@ -24309,7 +24309,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="F1041" t="n">
-        <v>0.620000004768372</v>
+        <v>0.600000023841858</v>
       </c>
       <c r="G1041" t="s">
         <v>7</v>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -27519,6 +27519,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1045">
+      <c r="A1045" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1045" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C1045" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>0.605000019073486</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>0.605000019073486</v>
+      </c>
+      <c r="F1045" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="H1045" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -27545,6 +27545,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1046">
+      <c r="A1046" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1046" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C1046" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>0.589999973773956</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>0.589999973773956</v>
+      </c>
+      <c r="F1046" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="H1046" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -27571,6 +27571,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1047">
+      <c r="A1047" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1047" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C1047" t="n">
+        <v>0.610000014305115</v>
+      </c>
+      <c r="D1047" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="E1047" t="n">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="F1047" t="n">
+        <v>0.610000014305115</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>0.610000014305115</v>
+      </c>
+      <c r="H1047" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -27597,6 +27597,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1048">
+      <c r="A1048" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1048" t="n">
+        <v>15500</v>
+      </c>
+      <c r="C1048" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="D1048" t="n">
+        <v>0.564999997615814</v>
+      </c>
+      <c r="E1048" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="F1048" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>0.574999988079071</v>
+      </c>
+      <c r="H1048" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -27675,6 +27675,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1051">
+      <c r="A1051" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1051" t="n">
+        <v>23500</v>
+      </c>
+      <c r="C1051" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>0.504999995231628</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>0.524999976158142</v>
+      </c>
+      <c r="F1051" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>0.519999980926514</v>
+      </c>
+      <c r="H1051" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -24607,8 +24607,31 @@
       <c r="E1054" t="n">
         <v>0.493999987840652</v>
       </c>
-      <c r="F1054"/>
+      <c r="F1054" t="n">
+        <v>0.493999987840652</v>
+      </c>
       <c r="G1054" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1055" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C1055" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="D1055" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="E1055" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="F1055"/>
+      <c r="G1055" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -24630,8 +24630,31 @@
       <c r="E1055" t="n">
         <v>0.469999998807907</v>
       </c>
-      <c r="F1055"/>
+      <c r="F1055" t="n">
+        <v>0.479999989271164</v>
+      </c>
       <c r="G1055" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1056" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1056" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>0.462000012397766</v>
+      </c>
+      <c r="F1056"/>
+      <c r="G1056" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -24653,8 +24653,31 @@
       <c r="E1056" t="n">
         <v>0.462000012397766</v>
       </c>
-      <c r="F1056"/>
+      <c r="F1056" t="n">
+        <v>0.5</v>
+      </c>
       <c r="G1056" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1057" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1057" t="n">
+        <v>0.479999989271164</v>
+      </c>
+      <c r="D1057" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="E1057" t="n">
+        <v>0.476000010967255</v>
+      </c>
+      <c r="F1057"/>
+      <c r="G1057" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -24676,8 +24676,31 @@
       <c r="E1057" t="n">
         <v>0.476000010967255</v>
       </c>
-      <c r="F1057"/>
+      <c r="F1057" t="n">
+        <v>0.479999989271164</v>
+      </c>
       <c r="G1057" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1058" t="n">
+        <v>16500</v>
+      </c>
+      <c r="C1058" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>0.458000004291534</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>0.469999998807907</v>
+      </c>
+      <c r="F1058"/>
+      <c r="G1058" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -24706,6 +24706,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1059">
+      <c r="A1059" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1059" t="n">
+        <v>11500</v>
+      </c>
+      <c r="C1059" t="n">
+        <v>0.451999992132187</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>0.439999997615814</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>0.451999992132187</v>
+      </c>
+      <c r="F1059" t="n">
+        <v>0.449999988079071</v>
+      </c>
+      <c r="G1059" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -27961,6 +27961,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1062">
+      <c r="A1062" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1062" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1062" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="F1062" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>0.407999992370605</v>
+      </c>
+      <c r="H1062" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -27987,6 +27987,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1063">
+      <c r="A1063" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1063" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1063" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="F1063" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>0.409999996423721</v>
+      </c>
+      <c r="H1063" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -31205,6 +31205,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1064">
+      <c r="A1064" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1064" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1064" t="n">
+        <v>0.393999993801117</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="F1064" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="H1064" t="n">
+        <v>15500</v>
+      </c>
+      <c r="I1064" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1065" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1065" t="n">
+        <v>0.38400000333786</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>0.38400000333786</v>
+      </c>
+      <c r="F1065" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="H1065" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1065" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -31263,6 +31263,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1066">
+      <c r="A1066" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1066" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1066" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>0.391999989748001</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>0.356000006198883</v>
+      </c>
+      <c r="F1066" t="n">
+        <v>0.356000006198883</v>
+      </c>
+      <c r="G1066" t="n">
+        <v>0.356000006198883</v>
+      </c>
+      <c r="H1066" t="n">
+        <v>28000</v>
+      </c>
+      <c r="I1066" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -31292,6 +31292,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1067">
+      <c r="A1067" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1067" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1067" t="n">
+        <v>0.360000014305115</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>0.36599999666214</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>0.34799998998642</v>
+      </c>
+      <c r="F1067" t="n">
+        <v>0.36599999666214</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>0.36599999666214</v>
+      </c>
+      <c r="H1067" t="n">
+        <v>35000</v>
+      </c>
+      <c r="I1067" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -31321,6 +31321,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1068">
+      <c r="A1068" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1068" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1068" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>0.351999998092651</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="F1068" t="n">
+        <v>0.36599999666214</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>0.36599999666214</v>
+      </c>
+      <c r="H1068" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I1068" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -31332,7 +31332,7 @@
         <v>0.349999994039536</v>
       </c>
       <c r="D1068" t="n">
-        <v>0.351999998092651</v>
+        <v>0.36599999666214</v>
       </c>
       <c r="E1068" t="n">
         <v>0.349999994039536</v>
@@ -31347,6 +31347,35 @@
         <v>2500</v>
       </c>
       <c r="I1068" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1069" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1069" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="F1069" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>0.349999994039536</v>
+      </c>
+      <c r="H1069" t="n">
+        <v>8500</v>
+      </c>
+      <c r="I1069" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -31379,6 +31379,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1070">
+      <c r="A1070" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1070" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1070" t="n">
+        <v>0.360000014305115</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>0.370000004768372</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>0.354000002145767</v>
+      </c>
+      <c r="F1070" t="n">
+        <v>0.354000002145767</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>0.354000002145767</v>
+      </c>
+      <c r="H1070" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1070" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -31408,6 +31408,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1071">
+      <c r="A1071" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1071" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1071" t="n">
+        <v>0.324000000953674</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>0.360000014305115</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>0.310000002384186</v>
+      </c>
+      <c r="F1071" t="n">
+        <v>0.360000014305115</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>0.360000014305115</v>
+      </c>
+      <c r="H1071" t="n">
+        <v>97000</v>
+      </c>
+      <c r="I1071" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -31437,6 +31437,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1072">
+      <c r="A1072" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1072" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1072" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>0.351999998092651</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="F1072" t="n">
+        <v>0.351999998092651</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>0.351999998092651</v>
+      </c>
+      <c r="H1072" t="n">
+        <v>10500</v>
+      </c>
+      <c r="I1072" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/YOLO.MI.xlsx
+++ b/data/YOLO.MI.xlsx
@@ -31466,6 +31466,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1073">
+      <c r="A1073" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1073" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1073" t="n">
+        <v>0.354000002145767</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>0.354000002145767</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="F1073" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>0.340000003576279</v>
+      </c>
+      <c r="H1073" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I1073" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
